--- a/sources/bryan_step9.xlsx
+++ b/sources/bryan_step9.xlsx
@@ -6505,11 +6505,6 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Z71" t="inlineStr">
         <is>
           <t>bcfea26d-eec1-4e77-a327-5ff22d064f6e</t>

--- a/sources/bryan_step9.xlsx
+++ b/sources/bryan_step9.xlsx
@@ -857,6 +857,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
@@ -919,6 +924,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
@@ -984,6 +994,11 @@
       <c r="Y8" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>e28da776-8eb0-403d-bcb0-31b6cdece7b8</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -9612,6 +9627,11 @@
           <t>hmmmhhhhmh</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
@@ -9659,6 +9679,11 @@
           <t>hmmmhhhm</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
@@ -9704,6 +9729,11 @@
       <c r="T110" t="inlineStr">
         <is>
           <t>hmmmhhmh</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>f4a77540-d285-4628-a209-f8f0a4fbebf3</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">

--- a/sources/bryan_step9.xlsx
+++ b/sources/bryan_step9.xlsx
@@ -417,38 +417,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC110"/>
+  <dimension ref="A1:AD110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col hidden="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col hidden="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col hidden="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col hidden="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="91" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col hidden="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="91" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,125 +482,130 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -616,57 +622,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Full Neck Swing</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Full Neck Swing</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>b9305946-440e-4903-82b1-bc4c3df38326</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>7a60b5b2-61b4-4b77-80af-0fea7d01437e</t>
         </is>
@@ -683,57 +689,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Gravity Brain Buster</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Gravity Brain Buster</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>d717f605-24ab-4840-846c-de9e8575434c</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>bd58b462-b3cb-44c1-9f51-0aad14b96fe3</t>
         </is>
@@ -750,57 +756,57 @@
           <t>FC+df,d,df+1+2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Chains of Misery</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Chains of Misery</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>10,8,27</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>10,8,27</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>b093725e-7374-4121-98c7-3db5b9c9719d</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>a0b39050-96c6-45bf-acbe-a9c34a9ad0d4</t>
         </is>
@@ -824,50 +830,55 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Gravity Blow</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Gravity Blow</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -891,50 +902,55 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Knee Blast</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Knee Blast</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -958,55 +974,60 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Hummer Neck Wringer</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Hummer Neck Wringer</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>e28da776-8eb0-403d-bcb0-31b6cdece7b8</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>e28da776-8eb0-403d-bcb0-31b6cdece7b8</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1043,125 +1064,130 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="Q11" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R11" s="1" t="inlineStr">
+      <c r="S11" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S11" s="1" t="inlineStr">
+      <c r="T11" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T11" s="1" t="inlineStr">
+      <c r="U11" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U11" s="1" t="inlineStr">
+      <c r="V11" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V11" s="1" t="inlineStr">
+      <c r="W11" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
+      <c r="X11" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X11" s="1" t="inlineStr">
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AA11" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
+      <c r="AC11" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC11" s="1" t="inlineStr">
+      <c r="AD11" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1178,77 +1204,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>35f29db2-f4fb-4d5d-a97b-8e7770d719e7</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>3c764eb1-6c7d-444d-a70e-7485c7014543</t>
         </is>
@@ -1265,77 +1291,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>86e78961-9af8-4761-b94b-fb7fb1d09e03</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>c165c102-c9f2-4935-a18f-9cf4c71878f8</t>
         </is>
@@ -1352,77 +1378,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>667b62c5-5abf-48cc-ba5f-845bb6631d16</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>d2baf28b-0785-4dc5-aec3-30fb192438d9</t>
         </is>
@@ -1439,77 +1465,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>c3ddeb7b-15d0-4f6a-a85a-79dd25d6fd80</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>4b650d97-d07a-4f27-9a5d-4dd9f573c489</t>
         </is>
@@ -1526,77 +1552,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>b2bde0a1-8aec-415b-a91c-e51a011c1128</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>eec91cfa-b65d-4d0b-a338-bb8f2cdfd6ae</t>
         </is>
@@ -1613,77 +1639,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>63af962c-a69d-4f16-ac7f-dc133c83d570</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>eef0d9e4-347d-4440-9aac-4aa18ccf61ed</t>
         </is>
@@ -1700,77 +1726,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>70e22adb-965f-4e08-ab78-b6b3f743974e</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>ee0814e5-7b27-42b4-892e-078928c4a95a</t>
         </is>
@@ -1787,77 +1813,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>456d3fcc-259f-4186-ae24-40c3412a6b0c</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>7edfd364-ae85-44a1-a2b3-302987ad8d85</t>
         </is>
@@ -1874,77 +1900,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>afa7373b-018c-4e3d-8e83-7b700298d529</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>17d65f06-1838-49e4-83e3-4976f6f5d325</t>
         </is>
@@ -1961,77 +1987,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>7814b49d-2859-41cf-af67-e8937c2190cd</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>befd123f-3c4c-4604-be21-d86897ba5408</t>
         </is>
@@ -2048,77 +2074,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>3e9e8100-7850-4797-b12b-958fdd149c85</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>b7926136-6224-47f4-897b-a74f72f33ea8</t>
         </is>
@@ -2135,77 +2161,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>b770e55f-9dd5-4aa8-80ae-cd5bf905f72b</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>c16d9c85-d0ee-447f-80ec-9b558d1c4d60</t>
         </is>
@@ -2222,77 +2248,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>b047018a-414b-4b02-95c0-7f7429b1ad9c</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>7deb3264-29cf-4f22-9d7e-3508ee85cc14</t>
         </is>
@@ -2309,77 +2335,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>f85571d3-3cd8-40b4-8c20-b01d3389e5c4</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>9da87bcc-55d4-4279-8266-802bc3f5f052</t>
         </is>
@@ -2396,77 +2422,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>50ec8a34-6a73-4b70-893c-30a7dd44b4b8</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>11775274-3512-4701-92fc-073d5001df83</t>
         </is>
@@ -2483,77 +2509,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>ba8a9c2b-5ab1-4d3f-99a7-9424b68c4a5b</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>ac32fbf4-7463-4727-b08b-dc9e40337b54</t>
         </is>
@@ -2570,77 +2596,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>4d291064-934c-47fc-8cd7-8cfaa463ea2a</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>cb5e6237-07d9-40a5-9f9b-829e6726e4b2</t>
         </is>
@@ -2657,77 +2683,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>79e25884-c58e-46e0-8a7b-aa07e21f5080</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>3e2b5743-3760-4a12-aa30-571d46e34910</t>
         </is>
@@ -2744,77 +2770,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>23f6952f-ac87-4795-bdd3-217cb1f1a1a9</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>17ef3895-af8c-4218-870b-075054fae33e</t>
         </is>
@@ -2831,77 +2857,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>f44de3ca-dc4e-4706-8ad1-703b0c7c4706</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>a5571e3f-6255-4f6e-bd0f-a52aad306e69</t>
         </is>
@@ -2918,77 +2944,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>0ab2f885-c903-4bff-b229-dd4e235004f9</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>04e8523a-2710-4bc5-ae92-cecd2e6fd4b4</t>
         </is>
@@ -3005,77 +3031,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>bae35a1a-63fd-42e1-9ed8-b53bb142a6cd</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>0d9f002a-771f-45e3-8a4b-a0bd91163854</t>
         </is>
@@ -3092,77 +3118,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-29</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-29</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>b7c419f2-3a6a-4a8a-a710-d6985cb8e15f</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>a431a443-7981-4a4a-8242-a392af2e1e2a</t>
         </is>
@@ -3179,77 +3205,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>db455aec-2405-49fb-a3fc-10a5aa018fb6</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>beb63903-16df-4d87-b0a3-b3b236fb60ee</t>
         </is>
@@ -3286,125 +3312,130 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="I38" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="K38" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K38" s="1" t="inlineStr">
+      <c r="L38" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
+      <c r="M38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M38" s="1" t="inlineStr">
+      <c r="N38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N38" s="1" t="inlineStr">
+      <c r="O38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O38" s="1" t="inlineStr">
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="Q38" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q38" s="1" t="inlineStr">
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R38" s="1" t="inlineStr">
+      <c r="S38" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S38" s="1" t="inlineStr">
+      <c r="T38" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T38" s="1" t="inlineStr">
+      <c r="U38" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U38" s="1" t="inlineStr">
+      <c r="V38" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V38" s="1" t="inlineStr">
+      <c r="W38" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
+      <c r="X38" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
+      <c r="Y38" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB38" s="1" t="inlineStr">
+      <c r="AC38" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC38" s="1" t="inlineStr">
+      <c r="AD38" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3421,92 +3452,92 @@
           <t>df+1 ,2</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Double Body Blow</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Double Body Blow</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>-4 -3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>-4 -3</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>+2 +4</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>+2 +4</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>+2 +9</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>+2 +9</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>10,16</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>10,16</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2f245bd0-ea44-4863-bbed-5b488bbac93e</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>99c752fa-48f1-456c-ac1b-29b6dd9c3643</t>
         </is>
@@ -3523,92 +3554,92 @@
           <t>DF+1 &lt;1 &lt;1 &lt;1 ,2</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Vulcan Cannon - Vulcan Punch</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Vulcan Cannon - Vulcan Punch</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-4 -13 -13 -13 -3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>-4 -13 -13 -13 -3</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+2 -7 -7 -7 +4</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+2 -7 -7 -7 +4</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+2 -7 -7 -7 +9</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>+2 -7 -7 -7 +9</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>10,15,12,11,16</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>10,15,12,11,16</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>mmmmm</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>mmmmm</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Vulcan Punch can do done after 1st, 2nd, 3rd or 4th punch.</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>8e800154-2bd7-4b69-aa8f-bd98a3877099</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>8eb834d2-a4bc-4046-ad7a-cb03061a378b</t>
         </is>
@@ -3625,87 +3656,87 @@
           <t>SS+1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Headhunter</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Headhunter</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>e85a5bf7-d61e-4dda-bbf5-3dfbb4376f76</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>e99ae26f-1a73-49ea-ae83-becb4e12f849</t>
         </is>
@@ -3722,92 +3753,92 @@
           <t>SS+1 ~2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Cheap Trick</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Cheap Trick</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>69677b35-c83b-4565-8a3f-b259b25fdf42</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>e9079d50-e81f-46d7-b1ce-e7f0ff8fce2a</t>
         </is>
@@ -3831,90 +3862,95 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>d+1+2; N+1+2; SS+1+2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Hammer Driver</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Hammer Driver</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>17 x</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>17 x</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>x -12</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>x -12</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>x +7</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>x +7</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>x KD</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>14,21</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>KS SLDc</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>dfe8481e-9168-42b5-a4c9-db7b858e8692</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>9ad6ad94-8df1-454d-bd10-de1b716eb649</t>
         </is>
@@ -3931,87 +3967,87 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Side Step Elbow</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Side Step Elbow</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>0269ca64-0e11-4f4e-971a-2fa1c0a0ecb9</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>73cb3848-9999-4273-bb45-c9f71b9d65de</t>
         </is>
@@ -4028,87 +4064,87 @@
           <t>1 ,2</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-1 -1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-1 -1</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>+7 +10</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>+7 +10</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+7 +10</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>+7 +10</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>6,8</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>6,8</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>41511d59-22a2-4225-a57f-aa684e88e67e</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>16ddd24a-fa26-4f31-b99b-bb7c72f74795</t>
         </is>
@@ -4125,87 +4161,87 @@
           <t>1 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>– Bruce Rush</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Double Punch – Bruce Rush</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-4 -7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-1 -1 -4 -7</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+7 +10 +7 KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>+7 +10 +7 KD</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>11,14</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>6,8,11,14</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>hhmm</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>ee3cc512-3af1-4c66-9cd3-fc88f63ec17c</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>a169ece9-31a1-49ba-aefd-0c4ef3a142e7</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>41511d59-22a2-4225-a57f-aa684e88e67e</t>
         </is>
@@ -4222,87 +4258,87 @@
           <t>1 ,2 ,1 ,4</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>– Bruce Low Rush</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Double Punch – Bruce Low Rush</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-4 -9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-1 -1 -4 -9</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+7 +10 +7 +2</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>+7 +10 +7 +2</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>11,12</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>6,8,11,12</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>hhml</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>913a9738-7a22-4f83-be45-621e6b19627a</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>3c74c040-2417-41bb-ae2f-36db6f78407a</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>41511d59-22a2-4225-a57f-aa684e88e67e</t>
         </is>
@@ -4319,87 +4355,87 @@
           <t>1 ,2 ,3</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>– Northern Lights</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Double Punch – Northern Lights</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-1 -1 -10</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+7 +10 +1</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>+7 +10 +1</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>6,8,13</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>hhl</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>115beaa7-f38f-40c2-bc00-fa3709e89114</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>bd621ced-45de-45e4-8352-1b68feff90ed</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>41511d59-22a2-4225-a57f-aa684e88e67e</t>
         </is>
@@ -4416,87 +4452,87 @@
           <t>1 ~4</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Punch Kick Cross</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Punch Kick Cross</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-1 -9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-1 -9</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>6,15</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>6,15</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>451d70ec-83a3-49eb-b67d-00bba77e25ec</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>8b1b9056-7d13-4063-a50e-69f6222c18dc</t>
         </is>
@@ -4513,97 +4549,97 @@
           <t>1 ~4 &lt;2 &lt;1 &lt;2</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>– Lair's Dance</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Punch Kick Cross – Lair's Dance</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-7 -6 -20</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-1 -9 -7 -6 -20</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>+4 KD KD</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+7 +2 +4 KD KD</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>+7 KD KD KD KD</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>21,17,21</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>6,15,21,17,21</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>hhhhh</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Crumple Stun when the 2nd Knuckle hits. The 1st Knuckle will Crumple stun on Counter Hit.</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>1342444f-ae69-462f-8a46-d6605e561a0d</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>4c8420c7-020e-4140-9418-fb702477eea7</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>451d70ec-83a3-49eb-b67d-00bba77e25ec</t>
         </is>
@@ -4620,82 +4656,92 @@
           <t>1 ~4 &lt;2 &lt;1~u</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>&lt;2&lt;1~d</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>1~4&lt;2&lt;1~d</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>– Side Step Lair's Dance</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Punch Kick Cross – Side Step Lair's Dance</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-1 -9</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>6,15,21</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>The Side Step cancels the 2nd hit.</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>49257cf6-08dd-4a8d-b5ab-b9693bcb0668</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>2ea29a08-7753-4a33-809e-ee65fa0c57a0</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>451d70ec-83a3-49eb-b67d-00bba77e25ec</t>
         </is>
@@ -4712,97 +4758,97 @@
           <t>1 ~4 &lt;2 &lt;1 &lt;4</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>– Cremation</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Punch Kick Cross – Cremation</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-7 -6 -5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-1 -9 -7 -6 -5</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>+4 KD KD</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>+7 +2 +4 KD KD</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>+7 KD KD KD KD</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>21,17,23</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>6,15,21,17,23</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>hhhhm</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Crumple Stun when the 2nd Knuckle hits. The 1st Knuckle will Crumple stun on Counter Hit.</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>b4aec949-e55f-4d29-ae67-58668c8f425b</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>3c8bd1d7-0b28-4be3-8819-ea9e5449e36a</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>451d70ec-83a3-49eb-b67d-00bba77e25ec</t>
         </is>
@@ -4819,92 +4865,92 @@
           <t>1 ~4 &lt;2 &lt;4</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>– Atomic Dance</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Punch Kick Cross – Atomic Dance</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-7 -5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-1 -9 -7 -5</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>+4 K</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>+7 +2 +4 K</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>+7 KD KD KD</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>21,23</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>6,15,21,23</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>hhhm</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>062658b3-231a-4f40-b4cd-4d7a1fe47248</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>d0f9daab-a6c9-45a6-85cd-fbc3ba4dbefd</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>451d70ec-83a3-49eb-b67d-00bba77e25ec</t>
         </is>
@@ -4921,87 +4967,87 @@
           <t>1 ~4 ,3 ,3</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>– Southern Cross</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Punch Kick Cross – Southern Cross</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-5 -6</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-1 -9 -5 -6</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>+7 +2 +6 +5</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+6 +5</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>+7 KD +6 +5</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>17,16</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>6,15,17,16</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>hhmh</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>cbf4d8fb-9637-40f5-9801-986d20851905</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>dcf08051-8889-4e29-93d6-56a2d37e5cfc</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>451d70ec-83a3-49eb-b67d-00bba77e25ec</t>
         </is>
@@ -5018,87 +5064,87 @@
           <t>WS+1+2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Short Upper</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Short Upper</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>41abdf75-99e7-43f1-9f78-e06cbc362efc</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>c797fd32-bd68-4486-b8b2-a4dacf4947a7</t>
         </is>
@@ -5115,97 +5161,97 @@
           <t>b+1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Snake Slam</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Snake Slam</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>8ee0655d-39c6-4460-ac0d-90800d86feb0</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>2372bac6-69b2-44ed-b943-93e0e6d2d3dd</t>
         </is>
@@ -5229,100 +5275,105 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>qcf+1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Snake Upper</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Snake Upper</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>When taggin in Alex or Roger they will do an automatic Animal Taunt.</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>728a94c7-8dbb-48dc-9358-e55404e835ff</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>ea2431ff-56c3-40e3-afe6-625e136de40e</t>
         </is>
@@ -5339,87 +5390,87 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Mach Breaker</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Mach Breaker</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>0394bf0c-2a51-4c6a-8887-0f6f1706526e</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>404cf7f1-4b29-4412-89f9-a6e2e5703aaf</t>
         </is>
@@ -5436,92 +5487,92 @@
           <t>SS+2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Shell Shock</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Shell Shock</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>OS</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>1f3a03eb-e7f5-42e5-b04d-29f627eab389</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>f229f0c7-f000-4f57-9c23-a332865a89f9</t>
         </is>
@@ -5545,85 +5596,90 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>db+2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>Stomach Lift</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Stomach Lift</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>c44cdf26-c445-40eb-a149-a8673df5d38c</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>e53edba9-7839-40fd-a2be-0c720eec5361</t>
         </is>
@@ -5640,92 +5696,92 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Vulcan Punch</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Vulcan Punch</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>eb128f1a-45eb-4c33-a60e-6b4149cd654f</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>6e0f44e8-4b82-41f2-828b-94ff12cb13d8</t>
         </is>
@@ -5742,97 +5798,97 @@
           <t>b+2 &lt;1 &lt;2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Doom Knuckles - Mach Punch</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Doom Knuckles - Mach Punch</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-10 -6 -20</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-10 -6 -20</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>+1 KD KD</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>+1 KD KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>16,17,21</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>16,17,21</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Crumple Stun when the 2nd Knuckle hits. The 1st Knuckle will Crumple stun on Counter Hit.</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>d499ae50-0f56-4bec-ab5d-3899a03188a2</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>4e9fe550-f184-406b-b12e-aeb3f119bfc4</t>
         </is>
@@ -5856,55 +5912,60 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>b+2&lt;1~d</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Doom Knuckles - Side Step</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Doom Knuckles - Side Step</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>The Side Step cancels the 2nd hit.</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>e8fa6607-2025-4965-98cc-8166e6b807aa</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>4c6abf37-eed6-42ed-9f91-b1aa46b7e8a6</t>
         </is>
@@ -5921,97 +5982,97 @@
           <t>b+2 &lt;1 &lt;4</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Doom Knuckles - Wolf Bite</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Doom Knuckles - Wolf Bite</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-10 -6 -5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-10 -6 -5</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>+1 KD KD</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>+1 KD KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>16,17,23</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>16,17,23</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Crumple Stun when the 2nd Knuckle hits. The 1st Knuckle will Crumple stun on Counter Hit.</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>d072869d-21af-4445-9495-2fab3eae2323</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>df193078-3316-4cd1-9d0b-3e2d09237df5</t>
         </is>
@@ -6028,92 +6089,92 @@
           <t>b+2 &lt;4</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Doom Knuckle - Wolf Bite</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Doom Knuckle - Wolf Bite</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-10 -5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-10 -5</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>+1 KD</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>+1 KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>16,23</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>16,23</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>83c395cb-a51b-4b07-b260-b1cb19bb3c48</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>4f49c7c4-1266-41bd-8f72-b6abc018bc7a</t>
         </is>
@@ -6130,57 +6191,57 @@
           <t>b+2 ~f+1</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Fake Out Doom Knuckle</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Fake Out Doom Knuckle</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>The 1st hit is cancelled.</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>2eecd2a8-82cc-4db0-9d20-222d69cefff3</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>5e853f4f-4b3d-4994-8dc8-4071db81d911</t>
         </is>
@@ -6197,52 +6258,52 @@
           <t>b+2 ~f+1 &lt;2</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>– Mach Punch</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Fake Out Doom Knuckle – Mach Punch</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>17,21</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>ac56dd5e-af9c-4532-b25d-ff7bd9161a0f</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>c3887a5f-38c0-421f-a095-161082f2afec</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>2eecd2a8-82cc-4db0-9d20-222d69cefff3</t>
         </is>
@@ -6259,52 +6320,62 @@
           <t>b+2 ~f+1,u</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>b+2~f+1,d</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>– Side Step Mach</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Fake Out Doom Knuckle – Side Step Mach</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>17,-</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>h-</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>401d34d7-130e-44ab-a6bd-7906966a4974</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>6bfa3afb-2c04-4e02-b923-610f2a6da7ad</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>2eecd2a8-82cc-4db0-9d20-222d69cefff3</t>
         </is>
@@ -6321,52 +6392,52 @@
           <t>b+2 ~f+1 &lt;4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>– Wolf Bite</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Fake Out Doom Knuckle – Wolf Bite</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>17,23</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>e6cbb30c-50f9-4c02-bbad-7c0e3a6df041</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>54eba542-8d6b-4089-9ad6-ce068d258812</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>2eecd2a8-82cc-4db0-9d20-222d69cefff3</t>
         </is>
@@ -6383,52 +6454,52 @@
           <t>qcb</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Sway</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Sway</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>1bf13b27-5d79-4a3b-8fb1-eb8962f0e583</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>72eff205-1149-4322-b203-ded19a26d268</t>
         </is>
@@ -6445,92 +6516,92 @@
           <t>qcb,N+2</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>– Chin Smash</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Sway – Chin Smash</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>-,21</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>-h</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>bcfea26d-eec1-4e77-a327-5ff22d064f6e</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>ec491a98-7e2e-48be-bb78-8072314000d4</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>1bf13b27-5d79-4a3b-8fb1-eb8962f0e583</t>
         </is>
@@ -6554,85 +6625,90 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>qcf+2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Gut Punch</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>53b44105-3280-4c1c-8a9a-4157c61157ba</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>50642d70-d82a-4379-bd7e-1a068981c625</t>
         </is>
@@ -6649,82 +6725,92 @@
           <t>WS+2 ~f+2</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>~b+2</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>WS+2~b+2</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>– Fisherman's Slam</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Gut Punch – Fisherman's Slam</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>18,21</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>Throw</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>mThrow</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>The Fisherman's Slam can only be done after the Gut Punch hits.</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>b4886337-31fe-4e97-b122-4df8b82ca2e8</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>9f1fd9b0-c4d1-4726-8b9b-65eaf20f1d2e</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AC73" t="inlineStr">
         <is>
           <t>53b44105-3280-4c1c-8a9a-4157c61157ba</t>
         </is>
@@ -6741,87 +6827,87 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Slash Kick</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Slash Kick</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>84a2a467-9179-475a-a7f2-3ca482839a6d</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>a6c4100c-5770-49fc-8422-4cfae0a1c9c7</t>
         </is>
@@ -6838,87 +6924,87 @@
           <t>3 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Gatling Rush</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Gatling Rush</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-4 +10 -16 -7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-4 +10 -16 -7</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>+7 +1 0 KD</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>+7 +1 0 KD</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>+7 +1 0 KD</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>+7 +1 0 KD</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>18,11,10,14</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>18,11,10,14</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>36f39ca8-6981-4412-a0f3-5fd7cdbfef9b</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>1e357278-8780-4c32-a1bb-8b75fa4b6ba5</t>
         </is>
@@ -6935,87 +7021,87 @@
           <t>3 ,2 ,1 ,4</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Bruce Special</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Bruce Special</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>-4 +10 -16 -9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>-4 +10 -16 -9</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>+7 +1 0 +2</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>+7 +1 0 +2</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>+7 +1 0 +2</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>+7 +1 0 +2</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>18,11,10,12</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>18,11,10,12</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>mmml</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>mmml</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>fcc3800c-96b6-41f1-b071-eb320fe158bd</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>53c3a4c2-dd60-4b21-9bfd-430416e67544</t>
         </is>
@@ -7032,87 +7118,87 @@
           <t>3 ,3</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Quick Spin Kicks</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Quick Spin Kicks</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-4 -6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>-4 -6</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>+7 +5</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>+7 +5</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>+7 +5</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>+7 +5</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>18,16</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>18,16</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>91303478-208c-4422-ac17-6ea31246dc2e</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>2614a316-00a7-4e19-b64d-c246097d2540</t>
         </is>
@@ -7136,85 +7222,90 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>uf+3</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>Rolling Driver</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Rolling Driver</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>1bf25a9a-c1c1-4da8-b1eb-04660cfe57bc</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>803e758c-c694-499b-bee9-ecc36a035340</t>
         </is>
@@ -7238,90 +7329,95 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>f,f,f+3</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Leaping Slash Kick</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>b95d51d1-c7e1-4e31-83be-c17dd92090b5</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>f68cd361-2902-4e63-a3a0-1fbab2ca7f7c</t>
         </is>
@@ -7338,92 +7434,92 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Snake Edge</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Snake Edge</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-29</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>-29</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>(-7_KD)</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>(-7_KD)</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>JG BS RC</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>7b17b7b9-d850-4fab-a7e9-19612bd90b9c</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>063cd42e-c4ea-4274-91f5-375337388217</t>
         </is>
@@ -7447,90 +7543,95 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>qcf+3</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>Hammer Knee</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Hammer Knee</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>7fd21828-5b58-4a29-9f58-51e8a5d9237c</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>03b2665e-4d78-4b6d-9b33-5a468842b297</t>
         </is>
@@ -7547,87 +7648,87 @@
           <t>WS+3 ,4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>– Twin Hammer Knee</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Hammer Knee – Twin Hammer Knee</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-7 -6</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>+4 +4</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>KD +4</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>22,16</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>170072df-4aa3-4de7-afc0-aaf3772b94b6</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>39d58288-1461-4306-be9e-9a9df7aafc91</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AC82" t="inlineStr">
         <is>
           <t>7fd21828-5b58-4a29-9f58-51e8a5d9237c</t>
         </is>
@@ -7644,87 +7745,87 @@
           <t>b+3</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Front Kick</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Front Kick</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>0002f0bb-25a7-4154-b9e5-4732accf8f67</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>adf40381-ec42-420d-b7e8-ad6e20743090</t>
         </is>
@@ -7741,87 +7842,87 @@
           <t>b+3 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>– Bruce Rush</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Front Kick – Bruce Rush</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>-4 -4 -7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>-6 -4 -4 -7</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>+7 +7 KD</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>+5 +7 +7 KD</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>+7 +7 KD</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>+5 +7 +7 KD</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>12,11,14</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>20,12,11,14</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>hhmm</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>66122d16-117b-4299-9aac-89b298550a0b</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>758bd822-4643-4a63-9739-e4aaab13f012</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
+      <c r="AC84" t="inlineStr">
         <is>
           <t>0002f0bb-25a7-4154-b9e5-4732accf8f67</t>
         </is>
@@ -7838,87 +7939,87 @@
           <t>b+3 ,2 ,1 ,4</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>– Run for Cover</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Front Kick – Run for Cover</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>-4 -4 -9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>-6 -4 -4 -9</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>+7 +7 +2</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>+5 +7 +7 +2</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>+7 +7 +2</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>+5 +7 +7 +2</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>12,11,12</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>20,12,11,12</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>hml</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>hhml</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>c86f3925-ae01-446a-af5f-16b9d899075f</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>231f96c7-a9f9-4d10-aa43-2899e19be11d</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
+      <c r="AC85" t="inlineStr">
         <is>
           <t>0002f0bb-25a7-4154-b9e5-4732accf8f67</t>
         </is>
@@ -7935,72 +8036,72 @@
           <t>b+3 ,4</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>– Knee</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Front Kick – Knee</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>20,12</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>da61aefe-00dd-4bba-88ff-2ab5c112f6cb</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>efdba0f4-51b7-4554-8931-01e316e9b60e</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
+      <c r="AC86" t="inlineStr">
         <is>
           <t>0002f0bb-25a7-4154-b9e5-4732accf8f67</t>
         </is>
@@ -8017,87 +8118,87 @@
           <t>d+3+4</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Thin Low Kick</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Thin Low Kick</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>053d6da6-00de-45db-9fe9-dd3438d9f174</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>0f94c9e4-a31e-46ab-b9c1-94617c1a2c46</t>
         </is>
@@ -8114,47 +8215,47 @@
           <t>WS+3+4</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Spin Kick</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Spin Kick</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>d769af42-c95a-42b8-88c8-a520911a72a8</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>aca9f9cf-7bd3-4f05-ae9d-645c788c6d9b</t>
         </is>
@@ -8171,87 +8272,87 @@
           <t>b+4</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Quick Knee</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Quick Knee</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>064fd456-4d60-410e-b268-55fa712025b4</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>5fe0df4d-692b-419a-8fa0-33b5d3f9dc6c</t>
         </is>
@@ -8275,90 +8376,95 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>uf+4</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>Orbital Heel</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Orbital Heel</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>0220adef-8413-4db1-8621-34de83dcd669</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>2df11746-874b-45f7-ac95-5afb698f6500</t>
         </is>
@@ -8375,87 +8481,87 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Power Axe</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Power Axe</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>2dd3a9d9-d6ca-4a43-8bbf-2695c86779ce</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>282f1f43-705b-4d1b-9ee6-833f96b82c11</t>
         </is>
@@ -8472,87 +8578,87 @@
           <t>f+4 ,3 ,4</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Running Blind</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Running Blind</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>-4 -7 -12</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>-4 -7 -12</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>+7 +4 -3</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>+7 +4 -3</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>KD +4 KD</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>KD +4 KD</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>18,14,18</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>18,14,18</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>hmh</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>hmh</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>630f45bf-4ae1-4fca-ab9c-a4e9479cca0a</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>fbc60da2-49d2-4d61-8444-cbc24ccab2af</t>
         </is>
@@ -8569,92 +8675,92 @@
           <t>b,b+4</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Orbital Flip Drop</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Orbital Flip Drop</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>5925868e-7cde-415f-8e1c-0c1cafa9d782</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t>4a9c0a54-6a3a-4b10-a982-da08859a6495</t>
         </is>
@@ -8671,87 +8777,87 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Mach Kick</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Mach Kick</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>4036b6ab-f550-429b-9c3b-6eafc677fc23</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>01a62387-1548-430d-9f18-e05c30878bf5</t>
         </is>
@@ -8768,47 +8874,47 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>High &amp; Mid Punch Parry</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>High &amp; Mid Punch Parry</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>ebf9bd72-bfd4-4b54-b37d-e5fa223920a3</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>14b8bdef-25c5-4576-a4ee-ba5da8cd91b5</t>
         </is>
@@ -8825,57 +8931,57 @@
           <t>b+1+2 ~2</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>– Mach Punch</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>High &amp; Mid Punch Parry – Mach Punch</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>-,30</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="U96" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>Right punch parry results in a Vulcan Punch, a left punch parry results in a Mach Punch.</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>1163c38e-ad32-43b7-8c0e-93530351066c</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>4ccc07cd-ea1d-4627-97c1-9c8345b1f3ac</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
+      <c r="AC96" t="inlineStr">
         <is>
           <t>ebf9bd72-bfd4-4b54-b37d-e5fa223920a3</t>
         </is>
@@ -8892,57 +8998,57 @@
           <t>b+1+2 ~2</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>– Vulcan Punch</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>High &amp; Mid Punch Parry – Vulcan Punch</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>-,22</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>Right punch parry results in a Vulcan Punch, a left punch parry results in a Mach Punch.</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>bb90285b-7717-496d-8b46-ac3acf90ef87</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>081e1b83-879f-484b-901b-0562034622c3</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>ebf9bd72-bfd4-4b54-b37d-e5fa223920a3</t>
         </is>
@@ -8966,45 +9072,50 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>db+2+4; d+1+3; d+2+4</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>Low Parry</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Low Parry</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="R98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="U98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>5f1be7cb-8213-42e7-a7ae-fe364cc3a665</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AB98" t="inlineStr">
         <is>
           <t>3a0329a9-a169-46a1-8d9e-9f508882512e</t>
         </is>
@@ -9021,87 +9132,87 @@
           <t>1+3+4</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Taunt</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Taunt</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>+16</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>+16</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>+19</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>+19</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>+19</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>+19</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>c8698cd6-eb6b-49cc-b5ef-ab1afa687761</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>229b8765-8bfd-40bc-bca8-3ccd6aa9eb2b</t>
         </is>
@@ -9138,125 +9249,130 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F102" s="1" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr">
+      <c r="H102" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H102" s="1" t="inlineStr">
+      <c r="I102" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I102" s="1" t="inlineStr">
+      <c r="J102" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J102" s="1" t="inlineStr">
+      <c r="K102" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K102" s="1" t="inlineStr">
+      <c r="L102" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L102" s="1" t="inlineStr">
+      <c r="M102" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M102" s="1" t="inlineStr">
+      <c r="N102" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N102" s="1" t="inlineStr">
+      <c r="O102" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O102" s="1" t="inlineStr">
+      <c r="P102" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="Q102" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q102" s="1" t="inlineStr">
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R102" s="1" t="inlineStr">
+      <c r="S102" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S102" s="1" t="inlineStr">
+      <c r="T102" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T102" s="1" t="inlineStr">
+      <c r="U102" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U102" s="1" t="inlineStr">
+      <c r="V102" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V102" s="1" t="inlineStr">
+      <c r="W102" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W102" s="1" t="inlineStr">
+      <c r="X102" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X102" s="1" t="inlineStr">
+      <c r="Y102" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y102" s="1" t="inlineStr">
+      <c r="Z102" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z102" s="1" t="inlineStr">
+      <c r="AA102" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA102" s="1" t="inlineStr">
+      <c r="AB102" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB102" s="1" t="inlineStr">
+      <c r="AC102" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC102" s="1" t="inlineStr">
+      <c r="AD102" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9273,77 +9389,77 @@
           <t>b+1+4</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Meteor Smash</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Meteor Smash</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
+      <c r="R103" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
+      <c r="T103" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="U103" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
+      <c r="AA103" t="inlineStr">
         <is>
           <t>5431b676-2691-4f7b-8d53-2a2f17a6acfe</t>
         </is>
       </c>
-      <c r="AA103" t="inlineStr">
+      <c r="AB103" t="inlineStr">
         <is>
           <t>e78795cc-21f0-4f8b-9ba9-43ab449f1ec1</t>
         </is>
@@ -9360,77 +9476,77 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Meteor Blow</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Meteor Blow</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="R104" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>6bc16e7d-73eb-45b5-abbe-4ec5aeeed033</t>
         </is>
       </c>
-      <c r="AA104" t="inlineStr">
+      <c r="AB104" t="inlineStr">
         <is>
           <t>b2c88db7-4618-4647-a77f-69052eae426d</t>
         </is>
@@ -9467,125 +9583,130 @@
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F107" s="1" t="inlineStr">
+      <c r="G107" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr">
+      <c r="H107" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H107" s="1" t="inlineStr">
+      <c r="I107" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I107" s="1" t="inlineStr">
+      <c r="J107" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J107" s="1" t="inlineStr">
+      <c r="K107" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K107" s="1" t="inlineStr">
+      <c r="L107" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L107" s="1" t="inlineStr">
+      <c r="M107" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M107" s="1" t="inlineStr">
+      <c r="N107" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N107" s="1" t="inlineStr">
+      <c r="O107" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O107" s="1" t="inlineStr">
+      <c r="P107" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P107" s="1" t="inlineStr">
+      <c r="Q107" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q107" s="1" t="inlineStr">
+      <c r="R107" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R107" s="1" t="inlineStr">
+      <c r="S107" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S107" s="1" t="inlineStr">
+      <c r="T107" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T107" s="1" t="inlineStr">
+      <c r="U107" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U107" s="1" t="inlineStr">
+      <c r="V107" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V107" s="1" t="inlineStr">
+      <c r="W107" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W107" s="1" t="inlineStr">
+      <c r="X107" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X107" s="1" t="inlineStr">
+      <c r="Y107" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y107" s="1" t="inlineStr">
+      <c r="Z107" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z107" s="1" t="inlineStr">
+      <c r="AA107" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA107" s="1" t="inlineStr">
+      <c r="AB107" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB107" s="1" t="inlineStr">
+      <c r="AC107" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC107" s="1" t="inlineStr">
+      <c r="AD107" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9602,42 +9723,42 @@
           <t>b+3 ,4 ,1 ,2 ,1 ,4 ,2 ,1 ,4 ,2</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
+      <c r="Q108" t="inlineStr">
         <is>
           <t>20,12,5,7,3,8,5,5,10,21</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr">
+      <c r="R108" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr">
+      <c r="S108" t="inlineStr">
         <is>
           <t>20,12,5,7,3,8,5,5,10,21</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
+      <c r="T108" t="inlineStr">
         <is>
           <t>hmmmhhhhmh</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="U108" t="inlineStr">
         <is>
           <t>hmmmhhhhmh</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
+      <c r="AA108" t="inlineStr">
         <is>
           <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
         </is>
       </c>
-      <c r="AA108" t="inlineStr">
+      <c r="AB108" t="inlineStr">
         <is>
           <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
+      <c r="AD108" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9654,42 +9775,42 @@
           <t>b+3 ,4 ,1 ,2 ,1 ,4 ,2 ,4</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>20,12,5,7,3,8,5,23</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr">
+      <c r="R109" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>20,12,5,7,3,8,5,23</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>hmmmhhhm</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t>hmmmhhhm</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
+      <c r="AA109" t="inlineStr">
         <is>
           <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
         </is>
       </c>
-      <c r="AA109" t="inlineStr">
+      <c r="AB109" t="inlineStr">
         <is>
           <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
+      <c r="AD109" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9706,42 +9827,42 @@
           <t>b+3 ,4 ,1 ,2 ,1 ,4 ,3 ,3</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>20,12,5,7,3,8,17,16</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="R110" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr">
+      <c r="S110" t="inlineStr">
         <is>
           <t>20,12,5,7,3,8,17,16</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
+      <c r="T110" t="inlineStr">
         <is>
           <t>hmmmhhmh</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="U110" t="inlineStr">
         <is>
           <t>hmmmhhmh</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>f4a77540-d285-4628-a209-f8f0a4fbebf3</t>
         </is>
       </c>
-      <c r="AA110" t="inlineStr">
+      <c r="AB110" t="inlineStr">
         <is>
           <t>f4a77540-d285-4628-a209-f8f0a4fbebf3</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
+      <c r="AD110" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
